--- a/test/fixture/snapshot/cli/sort-format/collection-mark/commander/commander-rare.xlsx
+++ b/test/fixture/snapshot/cli/sort-format/collection-mark/commander/commander-rare.xlsx
@@ -1074,21 +1074,24 @@
       <text>
         <r>
           <t xml:space="preserve">Border: black
-Finish: normal</t>
+Finish: normal
+Keywords:
+➤ Devoid</t>
         </r>
       </text>
     </comment>
     <comment ref="E11" authorId="0">
       <text>
         <r>
-          <t>Exile target nonland permanent. You lose 3 life.</t>
+          <t xml:space="preserve">Devoid (This card has no color.)
+Exile target nonland permanent. You may cast that card for as long as it remains exiled, and you may spend colorless mana as though it were mana of any color to cast that spell.</t>
         </r>
       </text>
     </comment>
     <comment ref="I11" authorId="0">
       <text>
         <r>
-          <t xml:space="preserve">➤ 1 generic
+          <t xml:space="preserve">➤ 2 generic
 ➤ 1 white
 ➤ 1 black</t>
         </r>
@@ -1105,11 +1108,35 @@
     <comment ref="E12" authorId="0">
       <text>
         <r>
+          <t>Exile target nonland permanent. You lose 3 life.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I12" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">➤ 1 generic
+➤ 1 white
+➤ 1 black</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D13" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">Border: black
+Finish: normal</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E13" authorId="0">
+      <text>
+        <r>
           <t>Destroy target permanent an opponent controls. Its controller may search their library for a basic land card, put it onto the battlefield, then shuffle.</t>
         </r>
       </text>
     </comment>
-    <comment ref="I12" authorId="0">
+    <comment ref="I13" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">➤ 1 black
@@ -1117,7 +1144,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D13" authorId="0">
+    <comment ref="D14" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Border: black
@@ -1127,14 +1154,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="E13" authorId="0">
+    <comment ref="E14" authorId="0">
       <text>
         <r>
           <t>Destroy target nonland permanent. Proliferate. (Choose any number of permanents and/or players, then give each another counter of each kind already there.)</t>
         </r>
       </text>
     </comment>
-    <comment ref="I13" authorId="0">
+    <comment ref="I14" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">➤ 2 generic
@@ -1143,7 +1170,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D14" authorId="0">
+    <comment ref="D15" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Loyalty: 5
@@ -1152,7 +1179,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E14" authorId="0">
+    <comment ref="E15" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Creatures you control have vigilance.
@@ -1161,7 +1188,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I14" authorId="0">
+    <comment ref="I15" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">➤ 2 generic
@@ -1170,7 +1197,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D15" authorId="0">
+    <comment ref="D16" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Border: black
@@ -1178,14 +1205,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="E15" authorId="0">
+    <comment ref="E16" authorId="0">
       <text>
         <r>
           <t>Return any number of permanent cards with different names from your graveyard to the battlefield.</t>
         </r>
       </text>
     </comment>
-    <comment ref="I15" authorId="0">
+    <comment ref="I16" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">➤ 2 white
@@ -1424,9 +1451,8 @@
     <comment ref="E5" authorId="0">
       <text>
         <r>
-          <t xml:space="preserve">As this land enters, you may reveal a Soldier card from your hand. This land enters tapped unless you revealed a Soldier card this way or you control a Soldier.
-{T}: Add {W} or {U}.
-{5}, {T}: Soldiers you control get +1/+1 until end of turn.</t>
+          <t xml:space="preserve">{T}: Add {C}. ({C} represents colorless mana.)
+{T}, Pay 1 life: Add one mana of any color. Spend this mana only to cast a spell with devoid.</t>
         </r>
       </text>
     </comment>
@@ -1441,12 +1467,29 @@
     <comment ref="E6" authorId="0">
       <text>
         <r>
+          <t xml:space="preserve">As this land enters, you may reveal a Soldier card from your hand. This land enters tapped unless you revealed a Soldier card this way or you control a Soldier.
+{T}: Add {W} or {U}.
+{5}, {T}: Soldiers you control get +1/+1 until end of turn.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D7" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">Border: black
+Finish: normal</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E7" authorId="0">
+      <text>
+        <r>
           <t xml:space="preserve">{T}: Add {C}.
 {1}, {T}: Add one mana of any color. If that mana is spent on a multicolored creature spell, that creature enters with an additional +1/+1 counter on it.</t>
         </r>
       </text>
     </comment>
-    <comment ref="D7" authorId="0">
+    <comment ref="D8" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Border: black
@@ -1456,27 +1499,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="E7" authorId="0">
+    <comment ref="E8" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">({T}: Add {W}, {B}, or {G}.)
 This land enters tapped.
 Cycling {3} ({3}, Discard this card: Draw a card.)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D8" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">Border: black
-Finish: normal</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E8" authorId="0">
-      <text>
-        <r>
-          <t>{T}, Pay 1 life: Add one mana of any color.</t>
         </r>
       </text>
     </comment>
@@ -1491,11 +1519,26 @@
     <comment ref="E9" authorId="0">
       <text>
         <r>
+          <t>{T}, Pay 1 life: Add one mana of any color.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D10" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">Border: black
+Finish: normal</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E10" authorId="0">
+      <text>
+        <r>
           <t>{T}, Pay 1 life, Sacrifice this land: Search your library for a basic land card, put it onto the battlefield, then shuffle.</t>
         </r>
       </text>
     </comment>
-    <comment ref="D10" authorId="0">
+    <comment ref="D11" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Border: borderless
@@ -1505,7 +1548,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0">
+    <comment ref="E11" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">({T}: Add {W}, {U}, or {B}.)
@@ -1514,7 +1557,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D11" authorId="0">
+    <comment ref="D12" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Border: black
@@ -1522,7 +1565,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E11" authorId="0">
+    <comment ref="E12" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">This land enters tapped unless you have two or more opponents.
@@ -1530,7 +1573,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D12" authorId="0">
+    <comment ref="D13" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Border: black
@@ -1540,7 +1583,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E12" authorId="0">
+    <comment ref="E13" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">({T}: Add {G}, {W}, or {U}.)
@@ -1549,7 +1592,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D13" authorId="0">
+    <comment ref="D14" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Border: black
@@ -1559,7 +1602,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E13" authorId="0">
+    <comment ref="E14" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">This land enters tapped.
@@ -1568,7 +1611,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D14" authorId="0">
+    <comment ref="D15" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Border: black
@@ -1578,7 +1621,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E14" authorId="0">
+    <comment ref="E15" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">({T}: Add {U} or {B}.)
@@ -1587,7 +1630,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D15" authorId="0">
+    <comment ref="D16" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Border: black
@@ -1595,7 +1638,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E15" authorId="0">
+    <comment ref="E16" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">This land enters tapped unless you have two or more opponents.
@@ -1603,7 +1646,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D16" authorId="0">
+    <comment ref="D17" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Border: black
@@ -1613,30 +1656,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="E16" authorId="0">
+    <comment ref="E17" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">({T}: Add {B}, {G}, or {U}.)
 This land enters tapped.
 Cycling {3} ({3}, Discard this card: Draw a card.)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D17" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">Border: black
-Finish: normal
-Keywords:
-➤ Channel</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E17" authorId="0">
-      <text>
-        <r>
-          <t xml:space="preserve">{T}: Add {G}.
-Channel — {1}{G}, Discard this card: Destroy target artifact, enchantment, or nonbasic land an opponent controls. That player may search their library for a land card with a basic land type, put it onto the battlefield, then shuffle. This ability costs {1} less to activate for each legendary creature you control.</t>
         </r>
       </text>
     </comment>
@@ -1653,8 +1678,8 @@
     <comment ref="E18" authorId="0">
       <text>
         <r>
-          <t xml:space="preserve">{T}: Add {W}.
-Channel — {2}{W}, Discard this card: It deals 4 damage to target attacking or blocking creature. This ability costs {1} less to activate for each legendary creature you control.</t>
+          <t xml:space="preserve">{T}: Add {G}.
+Channel — {1}{G}, Discard this card: Destroy target artifact, enchantment, or nonbasic land an opponent controls. That player may search their library for a land card with a basic land type, put it onto the battlefield, then shuffle. This ability costs {1} less to activate for each legendary creature you control.</t>
         </r>
       </text>
     </comment>
@@ -1662,14 +1687,17 @@
       <text>
         <r>
           <t xml:space="preserve">Border: black
-Finish: normal</t>
+Finish: normal
+Keywords:
+➤ Channel</t>
         </r>
       </text>
     </comment>
     <comment ref="E19" authorId="0">
       <text>
         <r>
-          <t>Each land is a Forest in addition to its other land types.</t>
+          <t xml:space="preserve">{T}: Add {W}.
+Channel — {2}{W}, Discard this card: It deals 4 damage to target attacking or blocking creature. This ability costs {1} less to activate for each legendary creature you control.</t>
         </r>
       </text>
     </comment>
@@ -1684,6 +1712,21 @@
     <comment ref="E20" authorId="0">
       <text>
         <r>
+          <t>Each land is a Forest in addition to its other land types.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D21" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">Border: black
+Finish: normal</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E21" authorId="0">
+      <text>
+        <r>
           <t xml:space="preserve">(As this Saga enters and after your draw step, add a lore counter. Sacrifice after III.)
 I — This Saga gains "{T}: Add {C}."
 II — This Saga gains "{2}, {T}: Create a 0/0 colorless Construct artifact creature token with 'This token gets +1/+1 for each artifact you control.'"
@@ -1696,7 +1739,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="477">
   <si>
     <t>Commander (Rare) - White</t>
   </si>
@@ -2586,6 +2629,30 @@
     <t>Open Simic Ascendancy</t>
   </si>
   <si>
+    <t>Abstruse Appropriation</t>
+  </si>
+  <si>
+    <t>mh3</t>
+  </si>
+  <si>
+    <t>Modern Horizons 3</t>
+  </si>
+  <si>
+    <t>177</t>
+  </si>
+  <si>
+    <t>{2}{W}{B}</t>
+  </si>
+  <si>
+    <t>B, W</t>
+  </si>
+  <si>
+    <t>0.22</t>
+  </si>
+  <si>
+    <t>Open Abstruse Appropriation</t>
+  </si>
+  <si>
     <t>Anguished Unmaking</t>
   </si>
   <si>
@@ -2601,9 +2668,6 @@
     <t>{1}{W}{B}</t>
   </si>
   <si>
-    <t>B, W</t>
-  </si>
-  <si>
     <t>2.07</t>
   </si>
   <si>
@@ -2815,6 +2879,24 @@
   </si>
   <si>
     <t>Open Bountiful Promenade</t>
+  </si>
+  <si>
+    <t>Corrupted Crossroads</t>
+  </si>
+  <si>
+    <t>ogw</t>
+  </si>
+  <si>
+    <t>Oath of the Gatewatch</t>
+  </si>
+  <si>
+    <t>169</t>
+  </si>
+  <si>
+    <t>0.20</t>
+  </si>
+  <si>
+    <t>Open Corrupted Crossroads</t>
   </si>
   <si>
     <t>Fortified Beachhead</t>
@@ -21459,7 +21541,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N215"/>
+  <dimension ref="A1:N216"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="33" customWidth="1"/>
@@ -21920,10 +22002,10 @@
         <v>300</v>
       </c>
       <c r="J11" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>301</v>
+        <v>195</v>
       </c>
       <c r="L11" s="13" t="s">
         <v>301</v>
@@ -21952,36 +22034,36 @@
         <v>74</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>200</v>
+        <v>305</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>201</v>
+        <v>306</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J12" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>245</v>
+        <v>301</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>245</v>
+        <v>301</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B13" s="7">
         <v>1</v>
@@ -21996,19 +22078,19 @@
         <v>74</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>310</v>
+        <v>200</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>311</v>
+        <v>201</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>119</v>
+        <v>312</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>258</v>
+        <v>313</v>
       </c>
       <c r="J13" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K13" s="7" t="s">
         <v>245</v>
@@ -22017,59 +22099,59 @@
         <v>245</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="B14" s="13">
+      <c r="A14" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="B14" s="7">
         <v>1</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>316</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="H14" s="13" t="s">
+      <c r="D14" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="I14" s="13" t="s">
+      <c r="G14" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="J14" s="13">
+      <c r="H14" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="J14" s="7">
         <v>4</v>
       </c>
-      <c r="K14" s="13" t="s">
+      <c r="K14" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="M14" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="L14" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="M14" s="13" t="s">
+      <c r="N14" s="7" t="s">
         <v>320</v>
-      </c>
-      <c r="N14" s="13" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B15" s="13">
         <v>1</v>
@@ -22078,54 +22160,82 @@
         <v>16</v>
       </c>
       <c r="D15" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>324</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>325</v>
+      </c>
+      <c r="J15" s="13">
+        <v>4</v>
+      </c>
+      <c r="K15" s="13" t="s">
+        <v>326</v>
+      </c>
+      <c r="L15" s="13" t="s">
+        <v>326</v>
+      </c>
+      <c r="M15" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="N15" s="13" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="B16" s="13">
+        <v>1</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E16" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F16" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="G15" s="13" t="s">
+      <c r="G16" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="H15" s="13" t="s">
-        <v>317</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="J15" s="13">
+      <c r="H16" s="13" t="s">
+        <v>324</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>330</v>
+      </c>
+      <c r="J16" s="13">
         <v>7</v>
       </c>
-      <c r="K15" s="13" t="s">
-        <v>324</v>
-      </c>
-      <c r="L15" s="13" t="s">
-        <v>324</v>
-      </c>
-      <c r="M15" s="13" t="s">
-        <v>325</v>
-      </c>
-      <c r="N15" s="13" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
+      <c r="K16" s="13" t="s">
+        <v>331</v>
+      </c>
+      <c r="L16" s="13" t="s">
+        <v>331</v>
+      </c>
+      <c r="M16" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="N16" s="13" t="s">
+        <v>333</v>
+      </c>
     </row>
     <row r="17" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
@@ -25310,6 +25420,22 @@
       <c r="L215" s="1"/>
       <c r="M215" s="1"/>
       <c r="N215" s="1"/>
+    </row>
+    <row r="216" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A216" s="1"/>
+      <c r="B216" s="1"/>
+      <c r="C216" s="1"/>
+      <c r="D216" s="1"/>
+      <c r="E216" s="1"/>
+      <c r="F216" s="1"/>
+      <c r="G216" s="1"/>
+      <c r="H216" s="1"/>
+      <c r="I216" s="1"/>
+      <c r="J216" s="1"/>
+      <c r="K216" s="1"/>
+      <c r="L216" s="1"/>
+      <c r="M216" s="1"/>
+      <c r="N216" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -25329,10 +25455,11 @@
     <hyperlink ref="N13" r:id="rId11"/>
     <hyperlink ref="N14" r:id="rId12"/>
     <hyperlink ref="N15" r:id="rId13"/>
+    <hyperlink ref="N16" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId15"/>
+  <legacyDrawing r:id="rId16"/>
 </worksheet>
 </file>
 
@@ -25357,7 +25484,7 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -25419,7 +25546,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="B3" s="15">
         <v>1</v>
@@ -25434,16 +25561,16 @@
         <v>132</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="J3" s="15">
         <v>4</v>
@@ -25455,15 +25582,15 @@
         <v>195</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="B4" s="11">
         <v>1</v>
@@ -25478,16 +25605,16 @@
         <v>132</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="J4" s="11">
         <v>4</v>
@@ -25499,15 +25626,15 @@
         <v>195</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="B5" s="13">
         <v>1</v>
@@ -25516,22 +25643,22 @@
         <v>16</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="J5" s="13">
         <v>2</v>
@@ -25543,15 +25670,15 @@
         <v>195</v>
       </c>
       <c r="M5" s="13" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="B6" s="7">
         <v>1</v>
@@ -25560,10 +25687,10 @@
         <v>16</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>89</v>
@@ -25572,10 +25699,10 @@
         <v>90</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="J6" s="7">
         <v>2</v>
@@ -25587,15 +25714,15 @@
         <v>195</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="B7" s="13">
         <v>1</v>
@@ -25616,10 +25743,10 @@
         <v>54</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="J7" s="13">
         <v>1</v>
@@ -25631,10 +25758,10 @@
         <v>195</v>
       </c>
       <c r="M7" s="13" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="N7" s="13" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -28875,7 +29002,7 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -28937,7 +29064,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="B3" s="7">
         <v>1</v>
@@ -28946,22 +29073,22 @@
         <v>16</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="J3" s="7">
         <v>4</v>
@@ -28973,10 +29100,10 @@
         <v>195</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -32194,7 +32321,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N220"/>
+  <dimension ref="A1:N221"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -32214,7 +32341,7 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -32276,7 +32403,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="B3" s="7">
         <v>1</v>
@@ -32285,19 +32412,19 @@
         <v>16</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="I3" s="7" t="s">
         <v>195</v>
@@ -32312,15 +32439,15 @@
         <v>214</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="B4" s="7">
         <v>1</v>
@@ -32329,10 +32456,10 @@
         <v>16</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>98</v>
@@ -32341,7 +32468,7 @@
         <v>99</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>195</v>
@@ -32353,18 +32480,18 @@
         <v>195</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B5" s="7">
         <v>1</v>
@@ -32373,19 +32500,19 @@
         <v>16</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="I5" s="7" t="s">
         <v>195</v>
@@ -32397,18 +32524,18 @@
         <v>195</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>288</v>
+        <v>195</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="B6" s="7">
         <v>1</v>
@@ -32417,19 +32544,19 @@
         <v>16</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>195</v>
@@ -32441,18 +32568,18 @@
         <v>195</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>195</v>
+        <v>288</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>184</v>
+        <v>390</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="B7" s="7">
         <v>1</v>
@@ -32461,19 +32588,19 @@
         <v>16</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>53</v>
+        <v>393</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>54</v>
+        <v>394</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>195</v>
@@ -32485,18 +32612,18 @@
         <v>195</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>324</v>
+        <v>195</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>387</v>
+        <v>184</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="B8" s="7">
         <v>1</v>
@@ -32505,19 +32632,19 @@
         <v>16</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>390</v>
+        <v>53</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>391</v>
+        <v>54</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>195</v>
@@ -32529,18 +32656,18 @@
         <v>195</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>195</v>
+        <v>331</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="B9" s="7">
         <v>1</v>
@@ -32549,19 +32676,19 @@
         <v>16</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>195</v>
@@ -32576,15 +32703,15 @@
         <v>195</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="B10" s="7">
         <v>1</v>
@@ -32593,19 +32720,19 @@
         <v>16</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>402</v>
+        <v>370</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>195</v>
@@ -32617,18 +32744,18 @@
         <v>195</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>406</v>
+        <v>195</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B11" s="7">
         <v>1</v>
@@ -32637,19 +32764,19 @@
         <v>16</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>363</v>
+        <v>415</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>161</v>
+        <v>418</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>195</v>
@@ -32661,18 +32788,18 @@
         <v>195</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>288</v>
+        <v>419</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="B12" s="7">
         <v>1</v>
@@ -32681,19 +32808,19 @@
         <v>16</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>415</v>
+        <v>370</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>416</v>
+        <v>161</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>195</v>
@@ -32705,18 +32832,18 @@
         <v>195</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>417</v>
+        <v>288</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="B13" s="7">
         <v>1</v>
@@ -32725,19 +32852,19 @@
         <v>16</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>363</v>
+        <v>428</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="I13" s="7" t="s">
         <v>195</v>
@@ -32749,18 +32876,18 @@
         <v>195</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>301</v>
+        <v>430</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="B14" s="7">
         <v>1</v>
@@ -32769,19 +32896,19 @@
         <v>16</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>427</v>
+        <v>370</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>200</v>
+        <v>434</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>201</v>
+        <v>435</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>195</v>
@@ -32793,18 +32920,18 @@
         <v>195</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>252</v>
+        <v>301</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="B15" s="7">
         <v>1</v>
@@ -32813,19 +32940,19 @@
         <v>16</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>363</v>
+        <v>440</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>89</v>
+        <v>200</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>90</v>
+        <v>201</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>195</v>
@@ -32837,18 +32964,18 @@
         <v>195</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>301</v>
+        <v>252</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>230</v>
+        <v>442</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
     </row>
     <row r="16" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="B16" s="7">
         <v>1</v>
@@ -32857,19 +32984,19 @@
         <v>16</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>435</v>
+        <v>370</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>195</v>
@@ -32881,106 +33008,106 @@
         <v>195</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>437</v>
+        <v>301</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>438</v>
+        <v>230</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
     </row>
     <row r="17" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>440</v>
-      </c>
-      <c r="B17" s="13">
+      <c r="A17" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="B17" s="7">
         <v>1</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>441</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>442</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>443</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>444</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>445</v>
-      </c>
-      <c r="I17" s="13" t="s">
+      <c r="D17" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="I17" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="J17" s="13">
+      <c r="J17" s="7">
         <v>0</v>
       </c>
-      <c r="K17" s="13" t="s">
+      <c r="K17" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="L17" s="13" t="s">
+      <c r="L17" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
+        <v>453</v>
+      </c>
+      <c r="B18" s="13">
+        <v>1</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>454</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>456</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>457</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>458</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="J18" s="13">
+        <v>0</v>
+      </c>
+      <c r="K18" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="L18" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="M17" s="13" t="s">
-        <v>446</v>
-      </c>
-      <c r="N17" s="13" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>448</v>
-      </c>
-      <c r="B18" s="7">
-        <v>1</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>441</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>442</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>443</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>444</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>449</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="J18" s="7">
-        <v>0</v>
-      </c>
-      <c r="K18" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="L18" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M18" s="7" t="s">
-        <v>450</v>
-      </c>
-      <c r="N18" s="7" t="s">
-        <v>451</v>
+      <c r="M18" s="13" t="s">
+        <v>459</v>
+      </c>
+      <c r="N18" s="13" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="19" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="B19" s="7">
         <v>1</v>
@@ -32989,19 +33116,19 @@
         <v>16</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>19</v>
+        <v>456</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>20</v>
+        <v>457</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>195</v>
@@ -33013,74 +33140,102 @@
         <v>195</v>
       </c>
       <c r="L19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="B20" s="7">
+        <v>1</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="I20" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="M19" s="7" t="s">
-        <v>454</v>
-      </c>
-      <c r="N19" s="7" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
-        <v>456</v>
-      </c>
-      <c r="B20" s="13">
+      <c r="J20" s="7">
+        <v>0</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="B21" s="13">
         <v>1</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C21" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>457</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>458</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>459</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>460</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>461</v>
-      </c>
-      <c r="I20" s="13" t="s">
+      <c r="D21" s="13" t="s">
+        <v>470</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>471</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="I21" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="J20" s="13">
+      <c r="J21" s="13">
         <v>0</v>
       </c>
-      <c r="K20" s="13" t="s">
+      <c r="K21" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="L20" s="13" t="s">
+      <c r="L21" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="M20" s="13" t="s">
-        <v>462</v>
-      </c>
-      <c r="N20" s="13" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
+      <c r="M21" s="13" t="s">
+        <v>475</v>
+      </c>
+      <c r="N21" s="13" t="s">
+        <v>476</v>
+      </c>
     </row>
     <row r="22" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
@@ -36265,6 +36420,22 @@
       <c r="L220" s="1"/>
       <c r="M220" s="1"/>
       <c r="N220" s="1"/>
+    </row>
+    <row r="221" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A221" s="1"/>
+      <c r="B221" s="1"/>
+      <c r="C221" s="1"/>
+      <c r="D221" s="1"/>
+      <c r="E221" s="1"/>
+      <c r="F221" s="1"/>
+      <c r="G221" s="1"/>
+      <c r="H221" s="1"/>
+      <c r="I221" s="1"/>
+      <c r="J221" s="1"/>
+      <c r="K221" s="1"/>
+      <c r="L221" s="1"/>
+      <c r="M221" s="1"/>
+      <c r="N221" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -36289,9 +36460,10 @@
     <hyperlink ref="N18" r:id="rId16"/>
     <hyperlink ref="N19" r:id="rId17"/>
     <hyperlink ref="N20" r:id="rId18"/>
+    <hyperlink ref="N21" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId20"/>
+  <legacyDrawing r:id="rId21"/>
 </worksheet>
 </file>